--- a/artfynd/A 17780-2024 artfynd.xlsx
+++ b/artfynd/A 17780-2024 artfynd.xlsx
@@ -2309,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117906827</v>
+        <v>117906822</v>
       </c>
       <c r="B16" t="n">
-        <v>74524</v>
+        <v>80136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,21 +2325,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1776</v>
+        <v>735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420830</v>
+        <v>420889</v>
       </c>
       <c r="R16" t="n">
-        <v>7046940</v>
+        <v>7046896</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,6 +2388,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På mossa/förna under lutande björk. Brant terräng.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117911918</v>
+        <v>117906827</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>74524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,41 +2432,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1776</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroksvalen NÖ, Jmt</t>
+          <t>Källremsan, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420825</v>
+        <v>420830</v>
       </c>
       <c r="R17" t="n">
-        <v>7046967</v>
+        <v>7046940</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,29 +2501,25 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2629,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117906822</v>
+        <v>117911918</v>
       </c>
       <c r="B19" t="n">
-        <v>80136</v>
+        <v>57287</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,44 +2645,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>735</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källremsan, Kall, Jmt</t>
+          <t>Kroksvalen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420889</v>
+        <v>420825</v>
       </c>
       <c r="R19" t="n">
-        <v>7046896</v>
+        <v>7046967</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2712,7 +2713,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På mossa/förna under lutande björk. Brant terräng.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2722,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Fredrik Larsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 17780-2024 artfynd.xlsx
+++ b/artfynd/A 17780-2024 artfynd.xlsx
@@ -2312,7 +2312,7 @@
         <v>117906822</v>
       </c>
       <c r="B16" t="n">
-        <v>80136</v>
+        <v>80138</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117906827</v>
+        <v>117911918</v>
       </c>
       <c r="B17" t="n">
-        <v>74524</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,44 +2432,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1776</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källremsan, Kall, Jmt</t>
+          <t>Kroksvalen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420830</v>
+        <v>420825</v>
       </c>
       <c r="R17" t="n">
-        <v>7046940</v>
+        <v>7046967</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,35 +2498,39 @@
           <t>2024-06-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Fredrik Larsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117911917</v>
+        <v>117906827</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>74526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,41 +2539,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1776</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroksvalen NÖ, Jmt</t>
+          <t>Källremsan, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421034</v>
+        <v>420830</v>
       </c>
       <c r="R18" t="n">
-        <v>7046604</v>
+        <v>7046940</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2604,39 +2608,35 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117911918</v>
+        <v>117911917</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420825</v>
+        <v>421034</v>
       </c>
       <c r="R19" t="n">
-        <v>7046967</v>
+        <v>7046604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 17780-2024 artfynd.xlsx
+++ b/artfynd/A 17780-2024 artfynd.xlsx
@@ -2526,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117911917</v>
+        <v>117911918</v>
       </c>
       <c r="B18" t="n">
         <v>57290</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421034</v>
+        <v>420825</v>
       </c>
       <c r="R18" t="n">
-        <v>7046604</v>
+        <v>7046967</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117911918</v>
+        <v>117911917</v>
       </c>
       <c r="B19" t="n">
         <v>57290</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420825</v>
+        <v>421034</v>
       </c>
       <c r="R19" t="n">
-        <v>7046967</v>
+        <v>7046604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 17780-2024 artfynd.xlsx
+++ b/artfynd/A 17780-2024 artfynd.xlsx
@@ -2526,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117911918</v>
+        <v>117911917</v>
       </c>
       <c r="B18" t="n">
         <v>57290</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420825</v>
+        <v>421034</v>
       </c>
       <c r="R18" t="n">
-        <v>7046967</v>
+        <v>7046604</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117911917</v>
+        <v>117911918</v>
       </c>
       <c r="B19" t="n">
         <v>57290</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421034</v>
+        <v>420825</v>
       </c>
       <c r="R19" t="n">
-        <v>7046604</v>
+        <v>7046967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
